--- a/TestData/omrBranchLogin.xlsx
+++ b/TestData/omrBranchLogin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Plywright_Wrkspace\omrBranchAutomationTask\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F26B7014-5050-43E9-8078-FC92E098F0E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467B80E9-939B-41F2-99E9-A1656501E059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,7 +438,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36.796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.296875" bestFit="1" customWidth="1"/>
@@ -453,7 +453,7 @@
     <col min="11" max="11" width="9.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -488,7 +488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -519,11 +519,8 @@
       <c r="J2" t="s">
         <v>20</v>
       </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -553,15 +550,12 @@
       </c>
       <c r="J3" t="s">
         <v>20</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:K1 A3:J3 A2:J2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/TestData/omrBranchLogin.xlsx
+++ b/TestData/omrBranchLogin.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Plywright_Wrkspace\omrBranchAutomationTask\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{467B80E9-939B-41F2-99E9-A1656501E059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D326B4C-15AF-4CC3-905B-BEC0DE765BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="omrBranchTest" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
   <si>
     <t>testScenario</t>
   </si>
@@ -55,9 +66,6 @@
     <t>noOfChild</t>
   </si>
   <si>
-    <t>Verify search hotels with all field</t>
-  </si>
-  <si>
     <t>ash.naveen.kv@gmail.com</t>
   </si>
   <si>
@@ -86,6 +94,78 @@
   </si>
   <si>
     <t>Verify search hotels with mandatory fields</t>
+  </si>
+  <si>
+    <t>VerifySearchHotelsWithAllField</t>
+  </si>
+  <si>
+    <t>Salutation</t>
+  </si>
+  <si>
+    <t>Mr</t>
+  </si>
+  <si>
+    <t>myFirstName</t>
+  </si>
+  <si>
+    <t>Naveenraj</t>
+  </si>
+  <si>
+    <t>myLastName</t>
+  </si>
+  <si>
+    <t>Rajendran</t>
+  </si>
+  <si>
+    <t>gstNumber</t>
+  </si>
+  <si>
+    <t>myCompanyName</t>
+  </si>
+  <si>
+    <t>companyAddress</t>
+  </si>
+  <si>
+    <t>Thoraipakkam</t>
+  </si>
+  <si>
+    <t>Greens Tech OMR Branch</t>
+  </si>
+  <si>
+    <t>9043592058</t>
+  </si>
+  <si>
+    <t>mobileNumber</t>
+  </si>
+  <si>
+    <t>9952040520</t>
+  </si>
+  <si>
+    <t>No special request</t>
+  </si>
+  <si>
+    <t>specialRequest</t>
+  </si>
+  <si>
+    <t>paymentType</t>
+  </si>
+  <si>
+    <t>debit_card</t>
+  </si>
+  <si>
+    <t>cardNumber</t>
+  </si>
+  <si>
+    <t>5555555555552222</t>
+  </si>
+  <si>
+    <t>cvv</t>
+  </si>
+  <si>
+    <t>222</t>
+  </si>
+  <si>
+    <t>Madurai</t>
   </si>
 </sst>
 </file>
@@ -109,7 +189,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -117,12 +197,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36.796875" bestFit="1" customWidth="1"/>
@@ -451,111 +548,216 @@
     <col min="9" max="9" width="10.69921875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.3984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.8984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" t="s">
-        <v>20</v>
-      </c>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K1 A3:J3 A2:J2" numberStoredAsText="1"/>
+    <ignoredError sqref="A3:J3 B2:D2 E1:H1 J1 F2:J2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>